--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573478477</v>
+        <v>46157.93114386967</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114386967</v>
+        <v>46157.93181055797</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181055797</v>
+        <v>46157.93404879715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404879715</v>
+        <v>46157.93722955084</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722955084</v>
+        <v>46158.28220811707</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220811707</v>
+        <v>46158.29697858266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29697858266</v>
+        <v>46158.29820406264</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820406264</v>
+        <v>46158.33391780475</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391780475</v>
+        <v>46158.36861600684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Вотинов- соц.работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861600684</v>
+        <v>46158.37292228138</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
